--- a/docs/downloads/经营分_河南省区__河南西片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__河南西片区_2026-10-18.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -2011,29 +2011,29 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7359436990858659849</t>
+          <t>7471147637970847807</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（洛阳应天门周王城广场店）</t>
+          <t>白玉兰商务酒店（洛阳龙门高铁站店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(洛阳应天门大卫天地店)</t>
+          <t>白玉兰酒店(洛阳龙门高铁站店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H17" t="n">
         <v>95</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>-5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2099,33 +2099,33 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>7542341710328629291</t>
+          <t>7359436990858659849</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（洛阳应天门九洲池店）</t>
+          <t>维也纳3好酒店（洛阳应天门周王城广场店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(洛阳应天门九洲池店)</t>
+          <t>维也纳3好酒店(洛阳应天门大卫天地店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H18" t="n">
         <v>95</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2135,13 +2135,13 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7443312211386173467</t>
+          <t>7542341710328629291</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳酒店（洛阳机场国家牡丹园旗舰店）</t>
+          <t>维也纳国际酒店（洛阳应天门九洲池店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳酒店(洛阳机场国家牡丹园旗舰店)</t>
+          <t>维也纳国际酒店(洛阳应天门九洲池店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2223,7 +2223,7 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
@@ -2235,7 +2235,7 @@
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2275,22 +2275,22 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7536810051504195625</t>
+          <t>7443312211386173467</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>麗枫酒店（洛阳应天门洛邑古城店）</t>
+          <t>维也纳酒店（洛阳机场国家牡丹园旗舰店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>麗枫酒店(洛阳应天门洛邑古城店)</t>
+          <t>维也纳酒店(洛阳机场国家牡丹园旗舰店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2317,13 +2317,13 @@
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2363,17 +2363,17 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7511155656196360246</t>
+          <t>7536810051504195625</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>希岸酒店（洛阳龙门高铁站店）</t>
+          <t>麗枫酒店（洛阳应天门洛邑古城店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>希岸酒店(龙门高铁站店)</t>
+          <t>麗枫酒店(洛阳应天门洛邑古城店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2382,14 +2382,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2399,19 +2399,19 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2451,17 +2451,17 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>6992776845766871048</t>
+          <t>7511155656196360246</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（洛阳博物馆龙门高铁站店）</t>
+          <t>希岸酒店（洛阳龙门高铁站店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>白玉兰酒店(洛阳市政府龙门高铁站店)</t>
+          <t>希岸酒店(龙门高铁站店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2473,11 +2473,11 @@
         <v>97</v>
       </c>
       <c r="I22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2493,13 +2493,13 @@
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2539,17 +2539,17 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7630752476929558571</t>
+          <t>6992776845766871048</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（洛阳洛邑古城启明南路地铁站店）</t>
+          <t>白玉兰商务酒店（洛阳博物馆龙门高铁站店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>白玉兰酒店(洛阳洛邑古城启明南路地铁站店)</t>
+          <t>白玉兰酒店(洛阳市政府龙门高铁站店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2575,13 +2575,13 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
       </c>
       <c r="O23" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P23" t="n">
         <v>30</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7090458625865189410</t>
+          <t>7630752476929558571</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>维也纳酒店（洛阳吉利店）</t>
+          <t>白玉兰商务酒店（洛阳洛邑古城启明南路地铁站店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>维也纳酒店(洛阳吉利店)</t>
+          <t>白玉兰酒店(洛阳洛邑古城启明南路地铁站店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -2663,7 +2663,7 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -2675,7 +2675,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2710,22 +2710,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>济源市</t>
+          <t>洛阳市</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>6601139689023883278</t>
+          <t>7090458625865189410</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>7天优品（济源天坛路信尧城市广场店）</t>
+          <t>维也纳酒店（洛阳吉利店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>7天优品(济源天坛路信尧城市广场店)</t>
+          <t>维也纳酒店(洛阳吉利店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2734,14 +2734,14 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>稳房源,附加分,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2763,13 +2763,13 @@
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
       </c>
       <c r="S25" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T25" t="n">
         <v>20</v>
@@ -2798,38 +2798,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>洛阳市</t>
+          <t>济源市</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>6601158375055034375</t>
+          <t>6601139689023883278</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>7天优品(洛阳牡丹广场地铁站王城公园店)</t>
+          <t>7天优品（济源天坛路信尧城市广场店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>7天优品酒店(洛阳牡丹广场地铁站店)</t>
+          <t>7天优品(济源天坛路信尧城市广场店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I26" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,附加分,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2839,25 +2839,25 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
       </c>
       <c r="O26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P26" t="n">
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T26" t="n">
         <v>20</v>
@@ -2891,29 +2891,29 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>6601140482472953860</t>
+          <t>6601158375055034375</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>7天优品Premium（洛阳火车站王城公园店）</t>
+          <t>7天优品(洛阳牡丹广场地铁站王城公园店)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7天优品Premium(洛阳火车站王城公园店)</t>
+          <t>7天优品酒店(洛阳牡丹广场地铁站店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -2927,13 +2927,13 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
       </c>
       <c r="O27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
@@ -2979,22 +2979,22 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7471147637970847807</t>
+          <t>6601140482472953860</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（洛阳龙门高铁站店）</t>
+          <t>7天优品Premium（洛阳火车站王城公园店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>白玉兰酒店(洛阳龙门高铁站店)</t>
+          <t>7天优品Premium(洛阳火车站王城公园店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3015,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
@@ -3027,7 +3027,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3441,7 +3441,7 @@
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H45" t="n">
@@ -4563,17 +4563,17 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>6601144057576032263</t>
+          <t>7593220618468722722</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>维也纳酒店（洛阳王城公园万达广场店）</t>
+          <t>维也纳酒店(5.0深化版洛阳汝阳杜康大道店)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>维也纳酒店(洛阳王城公园万达店)</t>
+          <t>维也纳酒店(洛阳汝阳杜康大道店)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4585,7 +4585,7 @@
         <v>105</v>
       </c>
       <c r="I46" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -4651,33 +4651,33 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>7376082006007875610</t>
+          <t>6601144057576032263</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>麗枫酒店（3.5洛阳栾川老君山店）</t>
+          <t>维也纳酒店（洛阳王城公园万达广场店）</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>麗枫酒店(洛阳栾川老君山店)</t>
+          <t>维也纳酒店(洛阳王城公园万达店)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H47" t="n">
         <v>105</v>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -4687,7 +4687,7 @@
         <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N47" t="n">
         <v>30</v>
@@ -4699,7 +4699,7 @@
         <v>30</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R47" t="n">
         <v>30</v>
@@ -4739,17 +4739,17 @@
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>7511607400000915497</t>
+          <t>7376082006007875610</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>麗枫酒店（洛阳龙门高铁站店）</t>
+          <t>麗枫酒店（3.5洛阳栾川老君山店）</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>麗枫酒店(洛阳龙门高铁站店)</t>
+          <t>麗枫酒店(洛阳栾川老君山店)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -4775,7 +4775,7 @@
         <v>10</v>
       </c>
       <c r="M48" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N48" t="n">
         <v>30</v>
@@ -4787,7 +4787,7 @@
         <v>30</v>
       </c>
       <c r="Q48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R48" t="n">
         <v>30</v>
@@ -4827,29 +4827,29 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>6601145726493788168</t>
+          <t>7511607400000915497</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>维也纳智好酒店（洛阳龙门高铁站开元大道关林景区店）</t>
+          <t>麗枫酒店（洛阳龙门高铁站店）</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>维也纳智好酒店(洛阳开元大道店)</t>
+          <t>麗枫酒店(洛阳龙门高铁站店)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I49" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>30</v>
       </c>
       <c r="Q49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R49" t="n">
         <v>30</v>
@@ -4915,17 +4915,17 @@
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>7593220618468722722</t>
+          <t>6601145726493788168</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0深化版洛阳汝阳杜康大道店)</t>
+          <t>维也纳智好酒店（洛阳龙门高铁站开元大道关林景区店）</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>维也纳酒店(洛阳汝阳杜康大道店)</t>
+          <t>维也纳智好酒店(洛阳开元大道店)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4937,7 +4937,7 @@
         <v>110</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>110</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
